--- a/data/empresas.xlsx
+++ b/data/empresas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/andres_ramirez_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres Ramirez\Documents\2026\automatizacionGmaill\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4338CBC-561C-4EF0-AF44-3457DD0A96EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2533BE-7364-41AC-9FDB-ECB31909552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2713CE67-7A45-453D-B01E-A4D3FC556313}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2713CE67-7A45-453D-B01E-A4D3FC556313}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Empresa</t>
   </si>
@@ -47,22 +47,184 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>LeoVegas</t>
-  </si>
-  <si>
-    <t>correo1@empresa.com</t>
-  </si>
-  <si>
-    <t>EveryMatrix</t>
-  </si>
-  <si>
-    <t>correo2@empresa.com</t>
-  </si>
-  <si>
-    <t>Betsson</t>
-  </si>
-  <si>
-    <t>correo3@empresa.com</t>
+    <t>Sixtema</t>
+  </si>
+  <si>
+    <t>rrhh@sixtema.es</t>
+  </si>
+  <si>
+    <t>CustomerTop</t>
+  </si>
+  <si>
+    <t>rrhh@customertop.es</t>
+  </si>
+  <si>
+    <t>AVC Tech Solutions</t>
+  </si>
+  <si>
+    <t>rrhh@avctechsolutions.com</t>
+  </si>
+  <si>
+    <t>BOTECH</t>
+  </si>
+  <si>
+    <t>rrhh@botech.info</t>
+  </si>
+  <si>
+    <t>Experian CheetahMail</t>
+  </si>
+  <si>
+    <t>rrhh@experian-cheetahmail.es</t>
+  </si>
+  <si>
+    <t>Abemon</t>
+  </si>
+  <si>
+    <t>rrhh@abemon.es</t>
+  </si>
+  <si>
+    <t>Bequant</t>
+  </si>
+  <si>
+    <t>jobs@bequant.com</t>
+  </si>
+  <si>
+    <t>Esri España</t>
+  </si>
+  <si>
+    <t>rrhh@esri.es</t>
+  </si>
+  <si>
+    <t>Voz.com</t>
+  </si>
+  <si>
+    <t>rrhh@voz.com</t>
+  </si>
+  <si>
+    <t>GlobalTel</t>
+  </si>
+  <si>
+    <t>rrhh@globaltel.es</t>
+  </si>
+  <si>
+    <t>Dayvo</t>
+  </si>
+  <si>
+    <t>rrhh@dayvo.com</t>
+  </si>
+  <si>
+    <t>Geotelecom</t>
+  </si>
+  <si>
+    <t>rrhh@geotelecom.es</t>
+  </si>
+  <si>
+    <t>HPS</t>
+  </si>
+  <si>
+    <t>rrhh@hps.es</t>
+  </si>
+  <si>
+    <t>STI Soluciones Tecnológicas</t>
+  </si>
+  <si>
+    <t>rrhh@sti-sl.es</t>
+  </si>
+  <si>
+    <t>Adtel</t>
+  </si>
+  <si>
+    <t>rrhh@adtel.es</t>
+  </si>
+  <si>
+    <t>Signe</t>
+  </si>
+  <si>
+    <t>rrhh@signe.es</t>
+  </si>
+  <si>
+    <t>VASS</t>
+  </si>
+  <si>
+    <t>rrhh@vass.es</t>
+  </si>
+  <si>
+    <t>GMV</t>
+  </si>
+  <si>
+    <t>careers@gmv.com</t>
+  </si>
+  <si>
+    <t>Plain Concepts</t>
+  </si>
+  <si>
+    <t>jobs@plainconcepts.com</t>
+  </si>
+  <si>
+    <t>Babel</t>
+  </si>
+  <si>
+    <t>careers@babelgroup.com</t>
+  </si>
+  <si>
+    <t>Netmind</t>
+  </si>
+  <si>
+    <t>jobs@netmind.net</t>
+  </si>
+  <si>
+    <t>Cognodata</t>
+  </si>
+  <si>
+    <t>jobs@cognodata.com</t>
+  </si>
+  <si>
+    <t>Izertis</t>
+  </si>
+  <si>
+    <t>empleo@izertis.com</t>
+  </si>
+  <si>
+    <t>Sngular</t>
+  </si>
+  <si>
+    <t>careers@sngular.com</t>
+  </si>
+  <si>
+    <t>knowmad mood</t>
+  </si>
+  <si>
+    <t>jobs@knowmadmood.com</t>
+  </si>
+  <si>
+    <t>OPPLUS</t>
+  </si>
+  <si>
+    <t>talent@opplus.es</t>
+  </si>
+  <si>
+    <t>BySidecar</t>
+  </si>
+  <si>
+    <t>careers@bysidecar.com</t>
+  </si>
+  <si>
+    <t>Factorial</t>
+  </si>
+  <si>
+    <t>info@factorial.co</t>
+  </si>
+  <si>
+    <t>CIEM Systems</t>
+  </si>
+  <si>
+    <t>info@ciemsystems.eu</t>
+  </si>
+  <si>
+    <t>Mentor VR</t>
+  </si>
+  <si>
+    <t>hola@mentor-vr.com</t>
   </si>
 </sst>
 </file>
@@ -461,8 +623,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538A5E57-67B4-4B95-851D-923762D11352}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="47.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -472,7 +637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -480,7 +645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -496,11 +661,254 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="mailto:correo1@empresa.com" xr:uid="{7FE7D221-6E0B-405F-AF88-0A1F8BBA0339}"/>
-    <hyperlink ref="B3" r:id="rId2" display="mailto:correo2@empresa.com" xr:uid="{10F59890-B1A4-433A-9E86-12A256EA43D5}"/>
-    <hyperlink ref="B4" r:id="rId3" display="mailto:correo3@empresa.com" xr:uid="{B5FC1DEB-223B-4957-8F9B-4BA186B3A48F}"/>
+    <hyperlink ref="B2" r:id="rId1" display="mailto:rrhh@sixtema.es" xr:uid="{54E8297C-D6EF-4016-9DB8-3A0B38EA6F06}"/>
+    <hyperlink ref="B3" r:id="rId2" display="mailto:rrhh@customertop.es" xr:uid="{A5685496-9C33-495C-BA57-82930C7FCA18}"/>
+    <hyperlink ref="B4" r:id="rId3" display="mailto:rrhh@avctechsolutions.com" xr:uid="{AB7668C5-6186-4328-9C5F-75172AB4CA7D}"/>
+    <hyperlink ref="B5" r:id="rId4" display="mailto:rrhh@botech.info" xr:uid="{E7A14F75-81FF-4299-A346-7AB552F6E1E4}"/>
+    <hyperlink ref="B6" r:id="rId5" display="mailto:rrhh@experian-cheetahmail.es" xr:uid="{50671CC5-EB3A-4651-A063-4013A7AA4106}"/>
+    <hyperlink ref="B7" r:id="rId6" display="mailto:rrhh@abemon.es" xr:uid="{88DEC044-E22B-415D-8925-25FA9B6B3F89}"/>
+    <hyperlink ref="B8" r:id="rId7" display="mailto:jobs@bequant.com" xr:uid="{7F40A34C-C0B2-4B9C-AAB8-3E7C687DCDEF}"/>
+    <hyperlink ref="B9" r:id="rId8" display="mailto:rrhh@esri.es" xr:uid="{B03B4345-A073-4EF9-8782-D77C0E5B35BD}"/>
+    <hyperlink ref="B10" r:id="rId9" display="mailto:rrhh@voz.com" xr:uid="{ED9B837D-3CBE-48D7-9E8C-38E6B4155BE8}"/>
+    <hyperlink ref="B11" r:id="rId10" display="mailto:rrhh@globaltel.es" xr:uid="{216C71A8-956E-4C0C-8A95-D0C72CDA26CE}"/>
+    <hyperlink ref="B12" r:id="rId11" display="mailto:rrhh@dayvo.com" xr:uid="{E3D5C827-1386-4001-BE71-413D89D15613}"/>
+    <hyperlink ref="B13" r:id="rId12" display="mailto:rrhh@geotelecom.es" xr:uid="{19EBF594-C7AC-4C92-85DA-26A183539119}"/>
+    <hyperlink ref="B14" r:id="rId13" display="mailto:rrhh@hps.es" xr:uid="{A63F91EF-011D-407F-83CB-D9E53952EFED}"/>
+    <hyperlink ref="B15" r:id="rId14" display="mailto:rrhh@sti-sl.es" xr:uid="{8C5E9749-D946-41FD-840B-21E969FC3C98}"/>
+    <hyperlink ref="B16" r:id="rId15" display="mailto:rrhh@adtel.es" xr:uid="{B1388B0A-37DC-47B8-A756-D4495EDF7080}"/>
+    <hyperlink ref="B17" r:id="rId16" display="mailto:rrhh@signe.es" xr:uid="{C4EF56FF-4722-4266-8EAA-EA6B3A0A7BD3}"/>
+    <hyperlink ref="B18" r:id="rId17" display="mailto:rrhh@vass.es" xr:uid="{D963AE44-8326-4079-A6A5-D7983CE8811C}"/>
+    <hyperlink ref="B19" r:id="rId18" display="mailto:careers@gmv.com" xr:uid="{D4A25C5D-CF19-404E-BC7D-48AE2506E1F2}"/>
+    <hyperlink ref="B20" r:id="rId19" display="mailto:jobs@plainconcepts.com" xr:uid="{DF18DF72-D1DA-4B04-B9E7-67E0C617A9D9}"/>
+    <hyperlink ref="B21" r:id="rId20" display="mailto:careers@babelgroup.com" xr:uid="{6CF55E7C-F947-4263-9BEA-CDD0B77BE194}"/>
+    <hyperlink ref="B22" r:id="rId21" display="mailto:jobs@netmind.net" xr:uid="{2FE6AB0D-C0A7-4C4D-B81D-B619DE158C67}"/>
+    <hyperlink ref="B23" r:id="rId22" display="mailto:jobs@cognodata.com" xr:uid="{9183010A-C839-4F3A-8CDB-F500CCF07A2F}"/>
+    <hyperlink ref="B24" r:id="rId23" display="mailto:empleo@izertis.com" xr:uid="{F194E098-6A21-4870-BA1C-DF9B4418FDA3}"/>
+    <hyperlink ref="B25" r:id="rId24" display="mailto:careers@sngular.com" xr:uid="{3800EEC8-8813-4ACA-8BEA-3E7EAFF542C0}"/>
+    <hyperlink ref="B26" r:id="rId25" display="mailto:jobs@knowmadmood.com" xr:uid="{259A173D-F9EF-4552-99CE-28E6AEE33A84}"/>
+    <hyperlink ref="B27" r:id="rId26" display="mailto:talent@opplus.es" xr:uid="{CC410333-7F06-4BD2-AC6C-D21C3E2CB79D}"/>
+    <hyperlink ref="B28" r:id="rId27" display="mailto:careers@bysidecar.com" xr:uid="{4A082D17-178B-44A2-9A2A-2EE85471EE5F}"/>
+    <hyperlink ref="B29" r:id="rId28" display="mailto:info@factorial.co" xr:uid="{E3E6FBBA-D929-4460-BA84-1451A60A8236}"/>
+    <hyperlink ref="B30" r:id="rId29" display="mailto:info@ciemsystems.eu" xr:uid="{9A90C928-FB88-4046-B335-57E2D89953C7}"/>
+    <hyperlink ref="B31" r:id="rId30" display="mailto:hola@mentor-vr.com" xr:uid="{FDFE9400-BF01-4343-9788-C73D8E2B0742}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/empresas.xlsx
+++ b/data/empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres Ramirez\Documents\2026\automatizacionGmaill\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2533BE-7364-41AC-9FDB-ECB31909552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D66A679-22F4-4063-B99D-993B9EE7E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2713CE67-7A45-453D-B01E-A4D3FC556313}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Empresa</t>
   </si>
@@ -47,184 +47,13 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>Sixtema</t>
+    <t>vio</t>
   </si>
   <si>
-    <t>rrhh@sixtema.es</t>
+    <t>tupuedes028@gmail.com</t>
   </si>
   <si>
-    <t>CustomerTop</t>
-  </si>
-  <si>
-    <t>rrhh@customertop.es</t>
-  </si>
-  <si>
-    <t>AVC Tech Solutions</t>
-  </si>
-  <si>
-    <t>rrhh@avctechsolutions.com</t>
-  </si>
-  <si>
-    <t>BOTECH</t>
-  </si>
-  <si>
-    <t>rrhh@botech.info</t>
-  </si>
-  <si>
-    <t>Experian CheetahMail</t>
-  </si>
-  <si>
-    <t>rrhh@experian-cheetahmail.es</t>
-  </si>
-  <si>
-    <t>Abemon</t>
-  </si>
-  <si>
-    <t>rrhh@abemon.es</t>
-  </si>
-  <si>
-    <t>Bequant</t>
-  </si>
-  <si>
-    <t>jobs@bequant.com</t>
-  </si>
-  <si>
-    <t>Esri España</t>
-  </si>
-  <si>
-    <t>rrhh@esri.es</t>
-  </si>
-  <si>
-    <t>Voz.com</t>
-  </si>
-  <si>
-    <t>rrhh@voz.com</t>
-  </si>
-  <si>
-    <t>GlobalTel</t>
-  </si>
-  <si>
-    <t>rrhh@globaltel.es</t>
-  </si>
-  <si>
-    <t>Dayvo</t>
-  </si>
-  <si>
-    <t>rrhh@dayvo.com</t>
-  </si>
-  <si>
-    <t>Geotelecom</t>
-  </si>
-  <si>
-    <t>rrhh@geotelecom.es</t>
-  </si>
-  <si>
-    <t>HPS</t>
-  </si>
-  <si>
-    <t>rrhh@hps.es</t>
-  </si>
-  <si>
-    <t>STI Soluciones Tecnológicas</t>
-  </si>
-  <si>
-    <t>rrhh@sti-sl.es</t>
-  </si>
-  <si>
-    <t>Adtel</t>
-  </si>
-  <si>
-    <t>rrhh@adtel.es</t>
-  </si>
-  <si>
-    <t>Signe</t>
-  </si>
-  <si>
-    <t>rrhh@signe.es</t>
-  </si>
-  <si>
-    <t>VASS</t>
-  </si>
-  <si>
-    <t>rrhh@vass.es</t>
-  </si>
-  <si>
-    <t>GMV</t>
-  </si>
-  <si>
-    <t>careers@gmv.com</t>
-  </si>
-  <si>
-    <t>Plain Concepts</t>
-  </si>
-  <si>
-    <t>jobs@plainconcepts.com</t>
-  </si>
-  <si>
-    <t>Babel</t>
-  </si>
-  <si>
-    <t>careers@babelgroup.com</t>
-  </si>
-  <si>
-    <t>Netmind</t>
-  </si>
-  <si>
-    <t>jobs@netmind.net</t>
-  </si>
-  <si>
-    <t>Cognodata</t>
-  </si>
-  <si>
-    <t>jobs@cognodata.com</t>
-  </si>
-  <si>
-    <t>Izertis</t>
-  </si>
-  <si>
-    <t>empleo@izertis.com</t>
-  </si>
-  <si>
-    <t>Sngular</t>
-  </si>
-  <si>
-    <t>careers@sngular.com</t>
-  </si>
-  <si>
-    <t>knowmad mood</t>
-  </si>
-  <si>
-    <t>jobs@knowmadmood.com</t>
-  </si>
-  <si>
-    <t>OPPLUS</t>
-  </si>
-  <si>
-    <t>talent@opplus.es</t>
-  </si>
-  <si>
-    <t>BySidecar</t>
-  </si>
-  <si>
-    <t>careers@bysidecar.com</t>
-  </si>
-  <si>
-    <t>Factorial</t>
-  </si>
-  <si>
-    <t>info@factorial.co</t>
-  </si>
-  <si>
-    <t>CIEM Systems</t>
-  </si>
-  <si>
-    <t>info@ciemsystems.eu</t>
-  </si>
-  <si>
-    <t>Mentor VR</t>
-  </si>
-  <si>
-    <t>hola@mentor-vr.com</t>
+    <t>tupuedes029@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -277,17 +106,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -623,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538A5E57-67B4-4B95-851D-923762D11352}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="47.85546875" customWidth="1"/>
@@ -638,278 +462,27 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="mailto:rrhh@sixtema.es" xr:uid="{54E8297C-D6EF-4016-9DB8-3A0B38EA6F06}"/>
-    <hyperlink ref="B3" r:id="rId2" display="mailto:rrhh@customertop.es" xr:uid="{A5685496-9C33-495C-BA57-82930C7FCA18}"/>
-    <hyperlink ref="B4" r:id="rId3" display="mailto:rrhh@avctechsolutions.com" xr:uid="{AB7668C5-6186-4328-9C5F-75172AB4CA7D}"/>
-    <hyperlink ref="B5" r:id="rId4" display="mailto:rrhh@botech.info" xr:uid="{E7A14F75-81FF-4299-A346-7AB552F6E1E4}"/>
-    <hyperlink ref="B6" r:id="rId5" display="mailto:rrhh@experian-cheetahmail.es" xr:uid="{50671CC5-EB3A-4651-A063-4013A7AA4106}"/>
-    <hyperlink ref="B7" r:id="rId6" display="mailto:rrhh@abemon.es" xr:uid="{88DEC044-E22B-415D-8925-25FA9B6B3F89}"/>
-    <hyperlink ref="B8" r:id="rId7" display="mailto:jobs@bequant.com" xr:uid="{7F40A34C-C0B2-4B9C-AAB8-3E7C687DCDEF}"/>
-    <hyperlink ref="B9" r:id="rId8" display="mailto:rrhh@esri.es" xr:uid="{B03B4345-A073-4EF9-8782-D77C0E5B35BD}"/>
-    <hyperlink ref="B10" r:id="rId9" display="mailto:rrhh@voz.com" xr:uid="{ED9B837D-3CBE-48D7-9E8C-38E6B4155BE8}"/>
-    <hyperlink ref="B11" r:id="rId10" display="mailto:rrhh@globaltel.es" xr:uid="{216C71A8-956E-4C0C-8A95-D0C72CDA26CE}"/>
-    <hyperlink ref="B12" r:id="rId11" display="mailto:rrhh@dayvo.com" xr:uid="{E3D5C827-1386-4001-BE71-413D89D15613}"/>
-    <hyperlink ref="B13" r:id="rId12" display="mailto:rrhh@geotelecom.es" xr:uid="{19EBF594-C7AC-4C92-85DA-26A183539119}"/>
-    <hyperlink ref="B14" r:id="rId13" display="mailto:rrhh@hps.es" xr:uid="{A63F91EF-011D-407F-83CB-D9E53952EFED}"/>
-    <hyperlink ref="B15" r:id="rId14" display="mailto:rrhh@sti-sl.es" xr:uid="{8C5E9749-D946-41FD-840B-21E969FC3C98}"/>
-    <hyperlink ref="B16" r:id="rId15" display="mailto:rrhh@adtel.es" xr:uid="{B1388B0A-37DC-47B8-A756-D4495EDF7080}"/>
-    <hyperlink ref="B17" r:id="rId16" display="mailto:rrhh@signe.es" xr:uid="{C4EF56FF-4722-4266-8EAA-EA6B3A0A7BD3}"/>
-    <hyperlink ref="B18" r:id="rId17" display="mailto:rrhh@vass.es" xr:uid="{D963AE44-8326-4079-A6A5-D7983CE8811C}"/>
-    <hyperlink ref="B19" r:id="rId18" display="mailto:careers@gmv.com" xr:uid="{D4A25C5D-CF19-404E-BC7D-48AE2506E1F2}"/>
-    <hyperlink ref="B20" r:id="rId19" display="mailto:jobs@plainconcepts.com" xr:uid="{DF18DF72-D1DA-4B04-B9E7-67E0C617A9D9}"/>
-    <hyperlink ref="B21" r:id="rId20" display="mailto:careers@babelgroup.com" xr:uid="{6CF55E7C-F947-4263-9BEA-CDD0B77BE194}"/>
-    <hyperlink ref="B22" r:id="rId21" display="mailto:jobs@netmind.net" xr:uid="{2FE6AB0D-C0A7-4C4D-B81D-B619DE158C67}"/>
-    <hyperlink ref="B23" r:id="rId22" display="mailto:jobs@cognodata.com" xr:uid="{9183010A-C839-4F3A-8CDB-F500CCF07A2F}"/>
-    <hyperlink ref="B24" r:id="rId23" display="mailto:empleo@izertis.com" xr:uid="{F194E098-6A21-4870-BA1C-DF9B4418FDA3}"/>
-    <hyperlink ref="B25" r:id="rId24" display="mailto:careers@sngular.com" xr:uid="{3800EEC8-8813-4ACA-8BEA-3E7EAFF542C0}"/>
-    <hyperlink ref="B26" r:id="rId25" display="mailto:jobs@knowmadmood.com" xr:uid="{259A173D-F9EF-4552-99CE-28E6AEE33A84}"/>
-    <hyperlink ref="B27" r:id="rId26" display="mailto:talent@opplus.es" xr:uid="{CC410333-7F06-4BD2-AC6C-D21C3E2CB79D}"/>
-    <hyperlink ref="B28" r:id="rId27" display="mailto:careers@bysidecar.com" xr:uid="{4A082D17-178B-44A2-9A2A-2EE85471EE5F}"/>
-    <hyperlink ref="B29" r:id="rId28" display="mailto:info@factorial.co" xr:uid="{E3E6FBBA-D929-4460-BA84-1451A60A8236}"/>
-    <hyperlink ref="B30" r:id="rId29" display="mailto:info@ciemsystems.eu" xr:uid="{9A90C928-FB88-4046-B335-57E2D89953C7}"/>
-    <hyperlink ref="B31" r:id="rId30" display="mailto:hola@mentor-vr.com" xr:uid="{FDFE9400-BF01-4343-9788-C73D8E2B0742}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{363548B5-DDBA-4EDF-A171-F8DA148AA1BC}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{4463A580-C9FA-46AA-A9A7-6B4CB654D1D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/data/empresas.xlsx
+++ b/data/empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres Ramirez\Documents\2026\automatizacionGmaill\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D66A679-22F4-4063-B99D-993B9EE7E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BB090F-EB24-4FF9-8572-D28F79142DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2713CE67-7A45-453D-B01E-A4D3FC556313}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Empresa</t>
   </si>
@@ -47,20 +47,89 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>vio</t>
-  </si>
-  <si>
-    <t>tupuedes028@gmail.com</t>
-  </si>
-  <si>
-    <t>tupuedes029@gmail.com</t>
+    <t>GMV</t>
+  </si>
+  <si>
+    <t>careers@gmv.com</t>
+  </si>
+  <si>
+    <t>Plain Concepts</t>
+  </si>
+  <si>
+    <t>jobs@plainconcepts.com</t>
+  </si>
+  <si>
+    <t>Babel</t>
+  </si>
+  <si>
+    <t>careers@babelgroup.com</t>
+  </si>
+  <si>
+    <t>Netmind</t>
+  </si>
+  <si>
+    <t>jobs@netmind.net</t>
+  </si>
+  <si>
+    <t>Cognodata</t>
+  </si>
+  <si>
+    <t>jobs@cognodata.com</t>
+  </si>
+  <si>
+    <t>Izertis</t>
+  </si>
+  <si>
+    <t>empleo@izertis.com</t>
+  </si>
+  <si>
+    <t>Sngular</t>
+  </si>
+  <si>
+    <t>careers@sngular.com</t>
+  </si>
+  <si>
+    <t>knowmad mood</t>
+  </si>
+  <si>
+    <t>jobs@knowmadmood.com</t>
+  </si>
+  <si>
+    <t>OPPLUS</t>
+  </si>
+  <si>
+    <t>talent@opplus.es</t>
+  </si>
+  <si>
+    <t>BySidecar</t>
+  </si>
+  <si>
+    <t>careers@bysidecar.com</t>
+  </si>
+  <si>
+    <t>Factorial</t>
+  </si>
+  <si>
+    <t>info@factorial.co</t>
+  </si>
+  <si>
+    <t>CIEM Systems</t>
+  </si>
+  <si>
+    <t>info@ciemsystems.eu</t>
+  </si>
+  <si>
+    <t>Mentor VR</t>
+  </si>
+  <si>
+    <t>hola@mentor-vr.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +149,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -106,12 +182,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -447,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538A5E57-67B4-4B95-851D-923762D11352}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="47.85546875" customWidth="1"/>
@@ -462,27 +543,126 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{363548B5-DDBA-4EDF-A171-F8DA148AA1BC}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{4463A580-C9FA-46AA-A9A7-6B4CB654D1D4}"/>
+    <hyperlink ref="B2" r:id="rId1" display="mailto:careers@gmv.com" xr:uid="{07547365-270F-462C-88FD-3FB6ACD694DC}"/>
+    <hyperlink ref="B3" r:id="rId2" display="mailto:jobs@plainconcepts.com" xr:uid="{34760BAF-70B2-4672-976A-31A6A86D8227}"/>
+    <hyperlink ref="B4" r:id="rId3" display="mailto:careers@babelgroup.com" xr:uid="{8266B585-926B-4E6E-A398-932A49E9B936}"/>
+    <hyperlink ref="B5" r:id="rId4" display="mailto:jobs@netmind.net" xr:uid="{D3494B5B-EF02-4D17-B2D8-30997BC3C99D}"/>
+    <hyperlink ref="B6" r:id="rId5" display="mailto:jobs@cognodata.com" xr:uid="{2D1FDBFF-7BA2-4043-A3BA-C5B4C286C6E0}"/>
+    <hyperlink ref="B7" r:id="rId6" display="mailto:empleo@izertis.com" xr:uid="{055D8107-DD63-4D8A-94A4-26F0D4AF181F}"/>
+    <hyperlink ref="B8" r:id="rId7" display="mailto:careers@sngular.com" xr:uid="{9BF36FC6-1A12-46C8-A325-33FF1F6993CB}"/>
+    <hyperlink ref="B9" r:id="rId8" display="mailto:jobs@knowmadmood.com" xr:uid="{A4B8887D-919E-4CD0-A28E-F2C6B6CACE61}"/>
+    <hyperlink ref="B10" r:id="rId9" display="mailto:talent@opplus.es" xr:uid="{DD05D849-D925-47D2-8BE2-550AB986B661}"/>
+    <hyperlink ref="B11" r:id="rId10" display="mailto:careers@bysidecar.com" xr:uid="{DD4A2C63-FAA3-4C09-ACC4-218143FFA4A3}"/>
+    <hyperlink ref="B12" r:id="rId11" display="mailto:info@factorial.co" xr:uid="{DF83BAB6-318B-412D-AD7D-1B14F24DE403}"/>
+    <hyperlink ref="B13" r:id="rId12" display="mailto:info@ciemsystems.eu" xr:uid="{D4410890-D25F-4952-8436-6C0714986FF6}"/>
+    <hyperlink ref="B14" r:id="rId13" display="mailto:hola@mentor-vr.com" xr:uid="{A0A2A92B-DF8B-48F1-8CD4-6CB91056F2C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
--- a/data/empresas.xlsx
+++ b/data/empresas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres Ramirez\Documents\2026\automatizacionGmaill\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BB090F-EB24-4FF9-8572-D28F79142DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B81B39-8926-47B8-9841-7DB64AC2E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2713CE67-7A45-453D-B01E-A4D3FC556313}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2713CE67-7A45-453D-B01E-A4D3FC556313}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="192">
   <si>
     <t>Empresa</t>
   </si>
@@ -47,89 +47,581 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>GMV</t>
-  </si>
-  <si>
-    <t>careers@gmv.com</t>
-  </si>
-  <si>
-    <t>Plain Concepts</t>
-  </si>
-  <si>
-    <t>jobs@plainconcepts.com</t>
-  </si>
-  <si>
-    <t>Babel</t>
-  </si>
-  <si>
-    <t>careers@babelgroup.com</t>
-  </si>
-  <si>
-    <t>Netmind</t>
-  </si>
-  <si>
-    <t>jobs@netmind.net</t>
-  </si>
-  <si>
-    <t>Cognodata</t>
-  </si>
-  <si>
-    <t>jobs@cognodata.com</t>
-  </si>
-  <si>
-    <t>Izertis</t>
-  </si>
-  <si>
-    <t>empleo@izertis.com</t>
-  </si>
-  <si>
     <t>Sngular</t>
   </si>
   <si>
-    <t>careers@sngular.com</t>
-  </si>
-  <si>
-    <t>knowmad mood</t>
-  </si>
-  <si>
-    <t>jobs@knowmadmood.com</t>
-  </si>
-  <si>
-    <t>OPPLUS</t>
-  </si>
-  <si>
-    <t>talent@opplus.es</t>
-  </si>
-  <si>
-    <t>BySidecar</t>
-  </si>
-  <si>
-    <t>careers@bysidecar.com</t>
-  </si>
-  <si>
-    <t>Factorial</t>
-  </si>
-  <si>
-    <t>info@factorial.co</t>
-  </si>
-  <si>
-    <t>CIEM Systems</t>
-  </si>
-  <si>
-    <t>info@ciemsystems.eu</t>
-  </si>
-  <si>
-    <t>Mentor VR</t>
-  </si>
-  <si>
-    <t>hola@mentor-vr.com</t>
+    <t>Movilges IT Consulting</t>
+  </si>
+  <si>
+    <t>Seltime</t>
+  </si>
+  <si>
+    <t>OteroQA</t>
+  </si>
+  <si>
+    <t>Aditelsa</t>
+  </si>
+  <si>
+    <t>Agilia Center</t>
+  </si>
+  <si>
+    <t>Integer Consulting</t>
+  </si>
+  <si>
+    <t>Bee Engineering ICT</t>
+  </si>
+  <si>
+    <t>Smart Consulting</t>
+  </si>
+  <si>
+    <t>IT People Innovation</t>
+  </si>
+  <si>
+    <t>Dellent Consulting</t>
+  </si>
+  <si>
+    <t>Sysmatch</t>
+  </si>
+  <si>
+    <t>Decskill</t>
+  </si>
+  <si>
+    <t>Ankix</t>
+  </si>
+  <si>
+    <t>Next Engineering</t>
+  </si>
+  <si>
+    <t>Mind Source</t>
+  </si>
+  <si>
+    <t>Match Profiler</t>
+  </si>
+  <si>
+    <t>KCS IT</t>
+  </si>
+  <si>
+    <t>Affinity</t>
+  </si>
+  <si>
+    <t>Aubay Portugal</t>
+  </si>
+  <si>
+    <t>PrimeIT Portugal</t>
+  </si>
+  <si>
+    <t>PrimeIT España</t>
+  </si>
+  <si>
+    <t>Rawson BPO</t>
+  </si>
+  <si>
+    <t>Plexus Tech</t>
+  </si>
+  <si>
+    <t>Zemsania LATAM</t>
+  </si>
+  <si>
+    <t>Zemsania Bilbao</t>
+  </si>
+  <si>
+    <t>Zemsania Valencia</t>
+  </si>
+  <si>
+    <t>Zemsania Sevilla</t>
+  </si>
+  <si>
+    <t>Infortec Consultores</t>
+  </si>
+  <si>
+    <t>Arelance</t>
+  </si>
+  <si>
+    <t>Qindel Group</t>
+  </si>
+  <si>
+    <t>Hasten Group</t>
+  </si>
+  <si>
+    <t>Babel Group</t>
+  </si>
+  <si>
+    <t>MNEMO</t>
+  </si>
+  <si>
+    <t>Dayvo Sistemas</t>
+  </si>
+  <si>
+    <t>Bitack Systems</t>
+  </si>
+  <si>
+    <t>SOTEC Consulting</t>
+  </si>
+  <si>
+    <t>Ditech Group</t>
+  </si>
+  <si>
+    <t>World Software Services</t>
+  </si>
+  <si>
+    <t>Euro-Funding</t>
+  </si>
+  <si>
+    <t>Cactus</t>
+  </si>
+  <si>
+    <t>CaixaBank Tech</t>
+  </si>
+  <si>
+    <t>Tier1</t>
+  </si>
+  <si>
+    <t>GTC Corporation</t>
+  </si>
+  <si>
+    <t>IMK Digital Agency</t>
+  </si>
+  <si>
+    <t>COD3NEXT</t>
+  </si>
+  <si>
+    <t>TWT-TS</t>
+  </si>
+  <si>
+    <t>Serem</t>
+  </si>
+  <si>
+    <t>SIAP Ingeniería</t>
+  </si>
+  <si>
+    <t>UF Tecnologia e Consultoria</t>
+  </si>
+  <si>
+    <t>Adentis Portugal</t>
+  </si>
+  <si>
+    <t>Create IT</t>
+  </si>
+  <si>
+    <t>NOX IT</t>
+  </si>
+  <si>
+    <t>ANO Software</t>
+  </si>
+  <si>
+    <t>DRAM Consultoria</t>
+  </si>
+  <si>
+    <t>Janela Digital</t>
+  </si>
+  <si>
+    <t>GBT Solutions</t>
+  </si>
+  <si>
+    <t>Vex Tech</t>
+  </si>
+  <si>
+    <t>Reditus</t>
+  </si>
+  <si>
+    <t>CADNEA / TECNEA</t>
+  </si>
+  <si>
+    <t>Craftable Software</t>
+  </si>
+  <si>
+    <t>Digidelta / Netscreen</t>
+  </si>
+  <si>
+    <t>QuickOps</t>
+  </si>
+  <si>
+    <t>MCC Consulting Group</t>
+  </si>
+  <si>
+    <t>Six-Factor</t>
+  </si>
+  <si>
+    <t>Noesis</t>
+  </si>
+  <si>
+    <t>Xelvin Portugal</t>
+  </si>
+  <si>
+    <t>EUC Inovação Portugal</t>
+  </si>
+  <si>
+    <t>Findmore Consulting</t>
+  </si>
+  <si>
+    <t>CodeWin</t>
+  </si>
+  <si>
+    <t>Ytech</t>
+  </si>
+  <si>
+    <t>Onile IT</t>
+  </si>
+  <si>
+    <t>Intelcia Portugal</t>
+  </si>
+  <si>
+    <t>DELAgroup</t>
+  </si>
+  <si>
+    <t>Neotalent Conclusion</t>
+  </si>
+  <si>
+    <t>TBFiles</t>
+  </si>
+  <si>
+    <t>Aurion First</t>
+  </si>
+  <si>
+    <t>Allied Testing</t>
+  </si>
+  <si>
+    <t>Odoo</t>
+  </si>
+  <si>
+    <t>Guardsquare</t>
+  </si>
+  <si>
+    <t>Saffron QA</t>
+  </si>
+  <si>
+    <t>Ahara</t>
+  </si>
+  <si>
+    <t>Less kW</t>
+  </si>
+  <si>
+    <t>Eco2Energias</t>
+  </si>
+  <si>
+    <t>Ultrarede</t>
+  </si>
+  <si>
+    <t>Luanju Climatización Industrial</t>
+  </si>
+  <si>
+    <t>Stockholm Precision Tools AB (SPT)</t>
+  </si>
+  <si>
+    <t>Satydal Comunicaciones</t>
+  </si>
+  <si>
+    <t>iRepack</t>
+  </si>
+  <si>
+    <t>recrutamento@movilges.com</t>
+  </si>
+  <si>
+    <t>rrhh@seltime.es</t>
+  </si>
+  <si>
+    <t>contact@oteroqa.com</t>
+  </si>
+  <si>
+    <t>talento@aditelsa.com</t>
+  </si>
+  <si>
+    <t>personas@agiliacenter.com</t>
+  </si>
+  <si>
+    <t>jobs@integer.pt</t>
+  </si>
+  <si>
+    <t>beatriz.pereira@integer.pt</t>
+  </si>
+  <si>
+    <t>cvbee@bee-eng.pt</t>
+  </si>
+  <si>
+    <t>work@smartconsulting.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@itpeople.pt</t>
+  </si>
+  <si>
+    <t>mariana.vales@itpeople.pt</t>
+  </si>
+  <si>
+    <t>margarida.monteiro@itpeople.pt</t>
+  </si>
+  <si>
+    <t>jobs@dellentconsulting.com</t>
+  </si>
+  <si>
+    <t>emprego@sysmatch.pt</t>
+  </si>
+  <si>
+    <t>leandra.rabottini@sysmatch.pt</t>
+  </si>
+  <si>
+    <t>joana.brito@decskill.com</t>
+  </si>
+  <si>
+    <t>ana.carvalho@decskill.com</t>
+  </si>
+  <si>
+    <t>emprego@ankix.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@nextengineering.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@mindsource.pt</t>
+  </si>
+  <si>
+    <t>emprego@m-profiler.com</t>
+  </si>
+  <si>
+    <t>rh@kcsit.pt</t>
+  </si>
+  <si>
+    <t>talentos@kcsit.pt</t>
+  </si>
+  <si>
+    <t>hr@affinity.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@aubay.pt</t>
+  </si>
+  <si>
+    <t>rh@primeit.pt</t>
+  </si>
+  <si>
+    <t>jfsramos@primeit.pt</t>
+  </si>
+  <si>
+    <t>talent@primeit.es</t>
+  </si>
+  <si>
+    <t>cv.linkedin@rawson-bpo.es</t>
+  </si>
+  <si>
+    <t>talento@plexus.es</t>
+  </si>
+  <si>
+    <t>rhlatam@zemsania.com</t>
+  </si>
+  <si>
+    <t>rrhh_bilbao@zemsania.com</t>
+  </si>
+  <si>
+    <t>rrhh_valencia@zemsania.com</t>
+  </si>
+  <si>
+    <t>rrhh_sevilla@zemsania.com</t>
+  </si>
+  <si>
+    <t>empleo@infortec.net</t>
+  </si>
+  <si>
+    <t>adriana.lopez@arelance.com</t>
+  </si>
+  <si>
+    <t>seleccion@qindel.com</t>
+  </si>
+  <si>
+    <t>esmeralda.gonzalez@grupohasten.com</t>
+  </si>
+  <si>
+    <t>personas@babelgroup.com</t>
+  </si>
+  <si>
+    <t>inmaculada.rodriguez@sngular.com</t>
+  </si>
+  <si>
+    <t>rrhh@mnemo.com</t>
+  </si>
+  <si>
+    <t>rrhh@dayvo.com</t>
+  </si>
+  <si>
+    <t>recursos.humanos@bitack-systems.com</t>
+  </si>
+  <si>
+    <t>irene.delama@sotec.es</t>
+  </si>
+  <si>
+    <t>cmedina@grupoditech.es</t>
+  </si>
+  <si>
+    <t>malvarez@wssgroup.com</t>
+  </si>
+  <si>
+    <t>seleccionef@euro-funding.com</t>
+  </si>
+  <si>
+    <t>hr_spain@cactus-now.com</t>
+  </si>
+  <si>
+    <t>cmcaicedog@caixabanktech.com</t>
+  </si>
+  <si>
+    <t>rrhh@tier1.es</t>
+  </si>
+  <si>
+    <t>trabajaconnosotros@gtccorporation.com</t>
+  </si>
+  <si>
+    <t>imk@imk.es</t>
+  </si>
+  <si>
+    <t>rrhh@cod3next.com</t>
+  </si>
+  <si>
+    <t>rrhh.twt.ts@twt-ts.com</t>
+  </si>
+  <si>
+    <t>contacto@serem.com</t>
+  </si>
+  <si>
+    <t>info@siapingenieria.es</t>
+  </si>
+  <si>
+    <t>cv@ufconsultoria.pt</t>
+  </si>
+  <si>
+    <t>work@adentis.pt</t>
+  </si>
+  <si>
+    <t>carreiras@create.pt</t>
+  </si>
+  <si>
+    <t>drh@nox-it.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@ano.pt</t>
+  </si>
+  <si>
+    <t>rh@dram.pt</t>
+  </si>
+  <si>
+    <t>rhumanos@janeladigital.com</t>
+  </si>
+  <si>
+    <t>leticia.bucker@gbtsolutions.pt</t>
+  </si>
+  <si>
+    <t>jobs@vextech.pt</t>
+  </si>
+  <si>
+    <t>red@reditus.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@cadnea.com</t>
+  </si>
+  <si>
+    <t>info@craftablesoftware.com</t>
+  </si>
+  <si>
+    <t>recrutamento@digidelta.pt</t>
+  </si>
+  <si>
+    <t>recruitment@quickops.pt</t>
+  </si>
+  <si>
+    <t>fma@mccconsultingroup.com</t>
+  </si>
+  <si>
+    <t>jca@mccconsultingroup.com</t>
+  </si>
+  <si>
+    <t>lcd@mccconsultingroup.com</t>
+  </si>
+  <si>
+    <t>recruitment@six-factor.com</t>
+  </si>
+  <si>
+    <t>jobs@noesis.pt</t>
+  </si>
+  <si>
+    <t>recruitment@xelvin.pt</t>
+  </si>
+  <si>
+    <t>info@eucinovacaoportugal.com</t>
+  </si>
+  <si>
+    <t>careers@findmore.eu</t>
+  </si>
+  <si>
+    <t>careers@findmore.pt</t>
+  </si>
+  <si>
+    <t>working@codewin.pt</t>
+  </si>
+  <si>
+    <t>gsantos@ytech.io</t>
+  </si>
+  <si>
+    <t>rh@onile-it.pt</t>
+  </si>
+  <si>
+    <t>recrutamento.portugal@intelcia.com</t>
+  </si>
+  <si>
+    <t>recrutamento@delagroup.pt</t>
+  </si>
+  <si>
+    <t>talent.pt@neotalentconclusion.com</t>
+  </si>
+  <si>
+    <t>recrutamento@tbfiles.com</t>
+  </si>
+  <si>
+    <t>andre.eusebio@aurionfirst.ai</t>
+  </si>
+  <si>
+    <t>hr@alliedtesting.careers</t>
+  </si>
+  <si>
+    <t>elde@odoo.com</t>
+  </si>
+  <si>
+    <t>jobs@guardsquare.com</t>
+  </si>
+  <si>
+    <t>ben@saffronqa.co.uk</t>
+  </si>
+  <si>
+    <t>emprego@sysmatch.com</t>
+  </si>
+  <si>
+    <t>your@nextengineering.pt</t>
+  </si>
+  <si>
+    <t>rh@ahara.pt</t>
+  </si>
+  <si>
+    <t>recrutamento@lesskw.com</t>
+  </si>
+  <si>
+    <t>geral@eco2energias.pt</t>
+  </si>
+  <si>
+    <t>recursos.humanos@ultrarede.pt</t>
+  </si>
+  <si>
+    <t>a.ramirez@luanju.com</t>
+  </si>
+  <si>
+    <t>jobs@sptab.com</t>
+  </si>
+  <si>
+    <t>fnavarro@satydal.es</t>
+  </si>
+  <si>
+    <t>rrhh@irepack.es</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,19 +638,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Carlito"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="2">
@@ -180,23 +665,23 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{322D581B-90E4-465F-BB3F-6D46F2AE625E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -528,13 +1013,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538A5E57-67B4-4B95-851D-923762D11352}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B102"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="47.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,127 +1027,816 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="48">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="24">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="36">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="36">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="36">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="36">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="24">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="24">
+      <c r="A12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="24">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="36">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="36">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="24">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="24">
+      <c r="A22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="24">
+      <c r="A26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="24">
+      <c r="A27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="24">
+      <c r="A28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="24">
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="24">
+      <c r="A30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="24">
+      <c r="A31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="24">
+      <c r="A32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="24">
+      <c r="A33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="24">
+      <c r="A34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="24">
+      <c r="A35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="36">
+      <c r="A36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="24">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="24">
+      <c r="A39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="24">
+      <c r="A40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="B41" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="24">
+      <c r="A43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="24">
+      <c r="A44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="36">
+      <c r="A45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="24">
+      <c r="A46" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="36">
+      <c r="A47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="24">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="24">
+      <c r="A50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="36">
+      <c r="A52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="36">
+      <c r="A53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="24">
+      <c r="A54" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="24">
+      <c r="A57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="60">
+      <c r="A58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="24">
+      <c r="A59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="24">
+      <c r="A62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="36">
+      <c r="A63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="24">
+      <c r="A64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="24">
+      <c r="A65" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="24">
+      <c r="A68" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="24">
+      <c r="A69" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="24">
+      <c r="A70" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="36">
+      <c r="A72" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="36">
+      <c r="A73" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="36">
+      <c r="A74" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="24">
+      <c r="A77" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="36">
+      <c r="A78" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="36">
+      <c r="A79" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="36">
+      <c r="A80" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="24">
+      <c r="A84" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="24">
+      <c r="A85" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="36">
+      <c r="A86" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="24">
+      <c r="A88" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="24">
+      <c r="A89" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="24">
+      <c r="A91" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="24">
+      <c r="A92" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B93" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="36">
+      <c r="A94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>27</v>
+      <c r="B94" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="24">
+      <c r="A97" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="48">
+      <c r="A99" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="60">
+      <c r="A100" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="36">
+      <c r="A101" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="mailto:careers@gmv.com" xr:uid="{07547365-270F-462C-88FD-3FB6ACD694DC}"/>
-    <hyperlink ref="B3" r:id="rId2" display="mailto:jobs@plainconcepts.com" xr:uid="{34760BAF-70B2-4672-976A-31A6A86D8227}"/>
-    <hyperlink ref="B4" r:id="rId3" display="mailto:careers@babelgroup.com" xr:uid="{8266B585-926B-4E6E-A398-932A49E9B936}"/>
-    <hyperlink ref="B5" r:id="rId4" display="mailto:jobs@netmind.net" xr:uid="{D3494B5B-EF02-4D17-B2D8-30997BC3C99D}"/>
-    <hyperlink ref="B6" r:id="rId5" display="mailto:jobs@cognodata.com" xr:uid="{2D1FDBFF-7BA2-4043-A3BA-C5B4C286C6E0}"/>
-    <hyperlink ref="B7" r:id="rId6" display="mailto:empleo@izertis.com" xr:uid="{055D8107-DD63-4D8A-94A4-26F0D4AF181F}"/>
-    <hyperlink ref="B8" r:id="rId7" display="mailto:careers@sngular.com" xr:uid="{9BF36FC6-1A12-46C8-A325-33FF1F6993CB}"/>
-    <hyperlink ref="B9" r:id="rId8" display="mailto:jobs@knowmadmood.com" xr:uid="{A4B8887D-919E-4CD0-A28E-F2C6B6CACE61}"/>
-    <hyperlink ref="B10" r:id="rId9" display="mailto:talent@opplus.es" xr:uid="{DD05D849-D925-47D2-8BE2-550AB986B661}"/>
-    <hyperlink ref="B11" r:id="rId10" display="mailto:careers@bysidecar.com" xr:uid="{DD4A2C63-FAA3-4C09-ACC4-218143FFA4A3}"/>
-    <hyperlink ref="B12" r:id="rId11" display="mailto:info@factorial.co" xr:uid="{DF83BAB6-318B-412D-AD7D-1B14F24DE403}"/>
-    <hyperlink ref="B13" r:id="rId12" display="mailto:info@ciemsystems.eu" xr:uid="{D4410890-D25F-4952-8436-6C0714986FF6}"/>
-    <hyperlink ref="B14" r:id="rId13" display="mailto:hola@mentor-vr.com" xr:uid="{A0A2A92B-DF8B-48F1-8CD4-6CB91056F2C6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId14"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>